--- a/outputs/01a032f3-e827-7bd1-8b8e-425918851986/2026-kokugo-sansu-day3.xlsx
+++ b/outputs/01a032f3-e827-7bd1-8b8e-425918851986/2026-kokugo-sansu-day3.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="1" r:id="R1f6100f22a594325"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="Rf1b0ac43bb1e42b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="3" r:id="Rc91c98437a1645dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="開催日" sheetId="4" r:id="R97a97b1febeb4cc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会場" sheetId="5" r:id="Rdf55ca05ad304de5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セッション" sheetId="6" r:id="R591fb0e3345e4a57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プログラム項目" sheetId="7" r:id="R98fcf5f6edfe4d9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="8" r:id="Ra56afc674b0a4375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="9" r:id="Rba2a630ccde94bba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="10" r:id="R4ab76f725bc54eb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="11" r:id="R86303dc4aee34baf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="1" r:id="R060a61f2975a4336"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R32132a2abde94ba3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="3" r:id="R05a129b7b91d483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="開催日" sheetId="4" r:id="Ra30d77c618b44d2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会場" sheetId="5" r:id="R80ebc443020b4fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セッション" sheetId="6" r:id="Re5f0a1233be64984"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プログラム項目" sheetId="7" r:id="Reef6a72387684c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="8" r:id="R0561ae8efc8d43db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="9" r:id="Rbe38802ce91748de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="10" r:id="R9451d75fa9374db1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="11" r:id="R73b9062dfce94baa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1343,60 +1343,140 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="17"/>
-      <x:c r="B6" s="17"/>
-      <x:c r="C6" s="17"/>
-      <x:c r="D6" s="17"/>
-      <x:c r="E6" s="17"/>
+      <x:c r="A6" s="17" t="str">
+        <x:v>1（最優先）</x:v>
+      </x:c>
+      <x:c r="B6" s="17" t="str">
+        <x:v>申込ページ</x:v>
+      </x:c>
+      <x:c r="C6" s="17" t="str">
+        <x:v>子どもと創る「国語×算数」授業研究会 Day3</x:v>
+      </x:c>
+      <x:c r="D6" s="17" t="str">
+        <x:v>https://www.toyokan.co.jp/products/kodomototukuru-jyugyo?variant=51131493744873</x:v>
+      </x:c>
+      <x:c r="E6" s="17" t="str">
+        <x:v>申込URL、PWA表示名、アイコン表記</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="17"/>
-      <x:c r="B7" s="17"/>
-      <x:c r="C7" s="17"/>
-      <x:c r="D7" s="17"/>
-      <x:c r="E7" s="17"/>
+      <x:c r="A7" s="17" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B7" s="17" t="str">
+        <x:v>公式サイト</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="str">
+        <x:v>リフレクション型国語科授業ー学びを主体化する国語学習サイクルー</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="str">
+        <x:v>https://www.toyokan.co.jp/products/5984</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="str">
+        <x:v>関連書籍の書誌情報・表紙</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="17"/>
-      <x:c r="B8" s="17"/>
-      <x:c r="C8" s="17"/>
-      <x:c r="D8" s="17"/>
-      <x:c r="E8" s="17"/>
+      <x:c r="A8" s="17" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="str">
+        <x:v>公式サイト</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="str">
+        <x:v>はじめての算数</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="str">
+        <x:v>https://www.toyokan.co.jp/products/5777</x:v>
+      </x:c>
+      <x:c r="E8" s="17" t="str">
+        <x:v>関連書籍の書誌情報・表紙</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="17"/>
-      <x:c r="B9" s="17"/>
-      <x:c r="C9" s="17"/>
-      <x:c r="D9" s="17"/>
-      <x:c r="E9" s="17"/>
+      <x:c r="A9" s="17" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B9" s="17" t="str">
+        <x:v>公式サイト</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>算数授業を左右する 教師の判断力</x:v>
+      </x:c>
+      <x:c r="D9" s="17" t="str">
+        <x:v>https://www.toyokan.co.jp/products/5084</x:v>
+      </x:c>
+      <x:c r="E9" s="17" t="str">
+        <x:v>関連書籍の書誌情報・表紙</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="17"/>
-      <x:c r="B10" s="17"/>
-      <x:c r="C10" s="17"/>
-      <x:c r="D10" s="17"/>
-      <x:c r="E10" s="17"/>
+      <x:c r="A10" s="17" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B10" s="17" t="str">
+        <x:v>公式サイト</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="str">
+        <x:v>「学びがい」のある学級ー子どもの声を引き出す教師の言葉がけ</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="str">
+        <x:v>https://www.toyokan.co.jp/products/4345</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="str">
+        <x:v>関連書籍の書誌情報・表紙</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="17"/>
-      <x:c r="B11" s="17"/>
-      <x:c r="C11" s="17"/>
-      <x:c r="D11" s="17"/>
-      <x:c r="E11" s="17"/>
+      <x:c r="A11" s="17" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B11" s="17" t="str">
+        <x:v>公式サイト</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="str">
+        <x:v>子どもの思考が動き出す 国語授業４つの発問</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="str">
+        <x:v>https://www.toyokan.co.jp/products/4034</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="str">
+        <x:v>関連書籍の書誌情報・表紙</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="17"/>
-      <x:c r="B12" s="17"/>
-      <x:c r="C12" s="17"/>
-      <x:c r="D12" s="17"/>
-      <x:c r="E12" s="17"/>
+      <x:c r="A12" s="17" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B12" s="17" t="str">
+        <x:v>公式サイト</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="str">
+        <x:v>算数授業を子どもと創る</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="str">
+        <x:v>https://www.toyokan.co.jp/products/3729</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="str">
+        <x:v>関連書籍の書誌情報・表紙</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="17"/>
-      <x:c r="B13" s="17"/>
-      <x:c r="C13" s="17"/>
-      <x:c r="D13" s="17"/>
-      <x:c r="E13" s="17"/>
+      <x:c r="A13" s="17" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B13" s="17" t="str">
+        <x:v>公式サイト</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>筑波附小の教育　子どもの学びが深まる理科授業デザイン</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="str">
+        <x:v>https://www.toyokan.co.jp/products/6346</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="str">
+        <x:v>関連書籍の書誌情報・表紙</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17"/>
@@ -1425,7 +1505,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0484813b39447aa"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7e62dac0f7f4a55"/>
 </x:worksheet>
 </file>
 
@@ -1508,7 +1588,7 @@
         <x:v>PWA表示名</x:v>
       </x:c>
       <x:c r="B7" s="25" t="str">
-        <x:v>国語×算数 Day3</x:v>
+        <x:v>創国算D3</x:v>
       </x:c>
       <x:c r="C7" s="17" t="str">
         <x:v>任意</x:v>
@@ -1522,7 +1602,7 @@
         <x:v>アイコン3文字</x:v>
       </x:c>
       <x:c r="B8" s="25" t="str">
-        <x:v>国算3</x:v>
+        <x:v>創国算</x:v>
       </x:c>
       <x:c r="C8" s="17" t="str">
         <x:v>任意</x:v>
@@ -1918,7 +1998,7 @@
     <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R725789cedfba4411"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd42042ba99694259"/>
 </x:worksheet>
 </file>
 
@@ -2059,7 +2139,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfecfd6dd06448f7"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra541ef464ec84236"/>
 </x:worksheet>
 </file>
 
@@ -2625,7 +2705,7 @@
     <x:mergeCell ref="A1:G1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf0fdf2ff7614225"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reeee7caadc184caa"/>
 </x:worksheet>
 </file>
 
@@ -3524,7 +3604,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38517f3105aa4d63"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd7c792bf79f4298"/>
 </x:worksheet>
 </file>
 
@@ -3561,10 +3641,18 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="24"/>
-      <x:c r="B4" s="24"/>
-      <x:c r="C4" s="24"/>
-      <x:c r="D4" s="24"/>
+      <x:c r="A4" s="24" t="str">
+        <x:v>参加申し込み</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="str">
+        <x:v>詳細・お申し込み</x:v>
+      </x:c>
+      <x:c r="C4" s="24" t="str">
+        <x:v>東洋館出版社の商品ページからお申し込みください。</x:v>
+      </x:c>
+      <x:c r="D4" s="24" t="str">
+        <x:v>https://www.toyokan.co.jp/products/kodomototukuru-jyugyo?variant=51131493744873</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25"/>
@@ -3801,66 +3889,150 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="24"/>
-      <x:c r="B4" s="24"/>
-      <x:c r="C4" s="24"/>
-      <x:c r="D4" s="24"/>
-      <x:c r="E4" s="24"/>
-      <x:c r="F4" s="24"/>
+      <x:c r="A4" s="24" t="str">
+        <x:v>リフレクション型国語科授業ー学びを主体化する国語学習サイクルー</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="str">
+        <x:v>白坂 洋一・香月 正登・小泉 芳男／編著</x:v>
+      </x:c>
+      <x:c r="C4" s="24" t="str">
+        <x:v>東洋館出版社</x:v>
+      </x:c>
+      <x:c r="D4" s="24" t="str">
+        <x:v>https://www.toyokan.co.jp/cdn/shop/files/6409_1_f0f83536-537d-419c-ae82-83a25e17234c.jpg?v=1770078225</x:v>
+      </x:c>
+      <x:c r="E4" s="24" t="str">
+        <x:v>リフレクション（省察）を中核とし、子どもが学びを「自分事」として引き受ける国語授業の具体像を示す。</x:v>
+      </x:c>
+      <x:c r="F4" s="24" t="str">
+        <x:v>https://www.toyokan.co.jp/products/5984</x:v>
+      </x:c>
       <x:c r="G4" s="24"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="25"/>
-      <x:c r="B5" s="25"/>
-      <x:c r="C5" s="25"/>
-      <x:c r="D5" s="25"/>
-      <x:c r="E5" s="25"/>
-      <x:c r="F5" s="25"/>
+      <x:c r="A5" s="25" t="str">
+        <x:v>はじめての算数</x:v>
+      </x:c>
+      <x:c r="B5" s="25" t="str">
+        <x:v>森本 隆史／編著</x:v>
+      </x:c>
+      <x:c r="C5" s="25" t="str">
+        <x:v>東洋館出版社</x:v>
+      </x:c>
+      <x:c r="D5" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/cdn/shop/files/5777_1.jpg?v=1738814903</x:v>
+      </x:c>
+      <x:c r="E5" s="25" t="str">
+        <x:v>算数の教科特性、授業準備、指導技術、評価、家庭学習まで、授業づくりの基礎・基本をコンパクトに解説。</x:v>
+      </x:c>
+      <x:c r="F5" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/products/5777</x:v>
+      </x:c>
       <x:c r="G5" s="25"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="25"/>
-      <x:c r="B6" s="25"/>
-      <x:c r="C6" s="25"/>
-      <x:c r="D6" s="25"/>
-      <x:c r="E6" s="25"/>
-      <x:c r="F6" s="25"/>
+      <x:c r="A6" s="25" t="str">
+        <x:v>算数授業を左右する 教師の判断力</x:v>
+      </x:c>
+      <x:c r="B6" s="25" t="str">
+        <x:v>森本 隆史／編著、算数授業を子どもと創る研究会／著</x:v>
+      </x:c>
+      <x:c r="C6" s="25" t="str">
+        <x:v>東洋館出版社</x:v>
+      </x:c>
+      <x:c r="D6" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/cdn/shop/products/product-124019.png?v=1692938855</x:v>
+      </x:c>
+      <x:c r="E6" s="25" t="str">
+        <x:v>21の場面×3つの判断で、子どもの学びの質を上げる教師の判断の選択肢を示す実践的な事例集。</x:v>
+      </x:c>
+      <x:c r="F6" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/products/5084</x:v>
+      </x:c>
       <x:c r="G6" s="25"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="25"/>
-      <x:c r="B7" s="25"/>
-      <x:c r="C7" s="25"/>
-      <x:c r="D7" s="25"/>
-      <x:c r="E7" s="25"/>
-      <x:c r="F7" s="25"/>
+      <x:c r="A7" s="25" t="str">
+        <x:v>「学びがい」のある学級ー子どもの声を引き出す教師の言葉がけ</x:v>
+      </x:c>
+      <x:c r="B7" s="25" t="str">
+        <x:v>白坂 洋一／著</x:v>
+      </x:c>
+      <x:c r="C7" s="25" t="str">
+        <x:v>東洋館出版社</x:v>
+      </x:c>
+      <x:c r="D7" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/cdn/shop/products/product-903415.jpg?v=1692938203</x:v>
+      </x:c>
+      <x:c r="E7" s="25" t="str">
+        <x:v>子どもの願いや問いから出発する学級づくりを、子どもの声を引き出す教師の言葉がけとともに紹介。</x:v>
+      </x:c>
+      <x:c r="F7" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/products/4345</x:v>
+      </x:c>
       <x:c r="G7" s="25"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="25"/>
-      <x:c r="B8" s="25"/>
-      <x:c r="C8" s="25"/>
-      <x:c r="D8" s="25"/>
-      <x:c r="E8" s="25"/>
-      <x:c r="F8" s="25"/>
+      <x:c r="A8" s="25" t="str">
+        <x:v>子どもの思考が動き出す 国語授業４つの発問</x:v>
+      </x:c>
+      <x:c r="B8" s="25" t="str">
+        <x:v>白坂 洋一／著</x:v>
+      </x:c>
+      <x:c r="C8" s="25" t="str">
+        <x:v>東洋館出版社</x:v>
+      </x:c>
+      <x:c r="D8" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/cdn/shop/products/4-574785.jpg?v=1692938516</x:v>
+      </x:c>
+      <x:c r="E8" s="25" t="str">
+        <x:v>子どもの思考の文脈を大切にする国語授業を、4つの発問と授業実践を通して解説。</x:v>
+      </x:c>
+      <x:c r="F8" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/products/4034</x:v>
+      </x:c>
       <x:c r="G8" s="25"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="25"/>
-      <x:c r="B9" s="25"/>
-      <x:c r="C9" s="25"/>
-      <x:c r="D9" s="25"/>
-      <x:c r="E9" s="25"/>
-      <x:c r="F9" s="25"/>
+      <x:c r="A9" s="25" t="str">
+        <x:v>算数授業を子どもと創る</x:v>
+      </x:c>
+      <x:c r="B9" s="25" t="str">
+        <x:v>森本 隆史／著</x:v>
+      </x:c>
+      <x:c r="C9" s="25" t="str">
+        <x:v>東洋館出版社</x:v>
+      </x:c>
+      <x:c r="D9" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/cdn/shop/products/product-910880.jpg?v=1692938856</x:v>
+      </x:c>
+      <x:c r="E9" s="25" t="str">
+        <x:v>教え込みから脱却し、言葉とかかわりを大切にしながら子どもと創る算数授業へ変える視点を紹介。</x:v>
+      </x:c>
+      <x:c r="F9" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/products/3729</x:v>
+      </x:c>
       <x:c r="G9" s="25"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="25"/>
-      <x:c r="B10" s="25"/>
-      <x:c r="C10" s="25"/>
-      <x:c r="D10" s="25"/>
-      <x:c r="E10" s="25"/>
-      <x:c r="F10" s="25"/>
+      <x:c r="A10" s="25" t="str">
+        <x:v>筑波附小の教育　子どもの学びが深まる理科授業デザイン</x:v>
+      </x:c>
+      <x:c r="B10" s="25" t="str">
+        <x:v>志田 正訓・鷲見 辰美・辻 健・富田 瑞枝／著</x:v>
+      </x:c>
+      <x:c r="C10" s="25" t="str">
+        <x:v>東洋館出版社</x:v>
+      </x:c>
+      <x:c r="D10" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/cdn/shop/files/6346_1.jpg?v=1770077603</x:v>
+      </x:c>
+      <x:c r="E10" s="25" t="str">
+        <x:v>小学校理科の全単元を網羅した36例の授業実践を通して、子どもの学びが深まる理科授業デザインを提案。</x:v>
+      </x:c>
+      <x:c r="F10" s="25" t="str">
+        <x:v>https://www.toyokan.co.jp/products/6346</x:v>
+      </x:c>
       <x:c r="G10" s="25"/>
     </x:row>
     <x:row r="11">

--- a/outputs/01a032f3-e827-7bd1-8b8e-425918851986/2026-kokugo-sansu-day3.xlsx
+++ b/outputs/01a032f3-e827-7bd1-8b8e-425918851986/2026-kokugo-sansu-day3.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="1" r:id="R060a61f2975a4336"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R32132a2abde94ba3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="3" r:id="R05a129b7b91d483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="開催日" sheetId="4" r:id="Ra30d77c618b44d2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会場" sheetId="5" r:id="R80ebc443020b4fa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セッション" sheetId="6" r:id="Re5f0a1233be64984"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プログラム項目" sheetId="7" r:id="Reef6a72387684c15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="8" r:id="R0561ae8efc8d43db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="9" r:id="Rbe38802ce91748de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="10" r:id="R9451d75fa9374db1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="11" r:id="R73b9062dfce94baa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="1" r:id="R2c5077f534b2403e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R3c5f3bdd2c674cd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="3" r:id="R5cc22383af614725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="開催日" sheetId="4" r:id="Rf72add8d1bf043a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会場" sheetId="5" r:id="R56e1d47198a1437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セッション" sheetId="6" r:id="R354f0b46cc664cd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プログラム項目" sheetId="7" r:id="Ra766f1b0957c4f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="8" r:id="R0f19e299c4e8493c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="9" r:id="R151209b534064d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="10" r:id="Rbe6b7ad3d0714679"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="11" r:id="Rb678416a2fa54439"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1360,7 +1360,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="17" t="str">
+      <x:c r="A7" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="17" t="str">
@@ -1377,7 +1377,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="17" t="str">
+      <x:c r="A8" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B8" s="17" t="str">
@@ -1394,7 +1394,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="17" t="str">
+      <x:c r="A9" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B9" s="17" t="str">
@@ -1411,7 +1411,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="17" t="str">
+      <x:c r="A10" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="17" t="str">
@@ -1428,7 +1428,7 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="17" t="str">
+      <x:c r="A11" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B11" s="17" t="str">
@@ -1445,7 +1445,7 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="17" t="str">
+      <x:c r="A12" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B12" s="17" t="str">
@@ -1462,7 +1462,7 @@
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="17" t="str">
+      <x:c r="A13" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B13" s="17" t="str">
@@ -1505,7 +1505,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7e62dac0f7f4a55"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53be18bf9ef245f2"/>
 </x:worksheet>
 </file>
 
@@ -1574,7 +1574,7 @@
         <x:v>アプリ名（短め）</x:v>
       </x:c>
       <x:c r="B6" s="25" t="str">
-        <x:v>国語×算数 Day3</x:v>
+        <x:v>国算創研2026</x:v>
       </x:c>
       <x:c r="C6" s="17" t="str">
         <x:v>必須</x:v>
@@ -1588,7 +1588,7 @@
         <x:v>PWA表示名</x:v>
       </x:c>
       <x:c r="B7" s="25" t="str">
-        <x:v>創国算D3</x:v>
+        <x:v>国算創研2026</x:v>
       </x:c>
       <x:c r="C7" s="17" t="str">
         <x:v>任意</x:v>
@@ -1599,253 +1599,267 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17" t="str">
-        <x:v>アイコン3文字</x:v>
+        <x:v>ブックマーク名</x:v>
       </x:c>
       <x:c r="B8" s="25" t="str">
-        <x:v>創国算</x:v>
+        <x:v>国算創研2026</x:v>
       </x:c>
       <x:c r="C8" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
-        <x:v>iconLabel。未入力ならlogoMain先頭3文字</x:v>
+        <x:v>bookmarkName。未入力ならアプリ名（短め）</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
-        <x:v>ロゴ補足</x:v>
+        <x:v>アイコン3文字</x:v>
       </x:c>
       <x:c r="B9" s="25" t="str">
-        <x:v>子どもと創る授業研究会</x:v>
+        <x:v>国算創</x:v>
       </x:c>
       <x:c r="C9" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D9" s="17" t="str">
-        <x:v>logoSub</x:v>
+        <x:v>iconLabel。未入力ならlogoMain先頭3文字</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
-        <x:v>テーマ</x:v>
+        <x:v>ロゴ補足</x:v>
       </x:c>
       <x:c r="B10" s="25" t="str">
-        <x:v>教科書から「定番教材」の授業をどう創るのか？</x:v>
+        <x:v>子どもと創る授業研究会</x:v>
       </x:c>
       <x:c r="C10" s="17" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="D10" s="17" t="str">
-        <x:v>theme。サブテーマを含む全文</x:v>
+        <x:v>logoSub</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
-        <x:v>会場名</x:v>
+        <x:v>テーマ</x:v>
       </x:c>
       <x:c r="B11" s="25" t="str">
-        <x:v>筑波大学附属小学校</x:v>
+        <x:v>教科書から「定番教材」の授業をどう創るのか？</x:v>
       </x:c>
       <x:c r="C11" s="17" t="str">
         <x:v>必須</x:v>
       </x:c>
       <x:c r="D11" s="17" t="str">
-        <x:v>venueName。オンラインの場合も資料表記に従う</x:v>
+        <x:v>theme。サブテーマを含む全文</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
-        <x:v>開催日（表示用）</x:v>
+        <x:v>会場名</x:v>
       </x:c>
       <x:c r="B12" s="25" t="str">
-        <x:v>2026年9月6日(日) 10:00〜15:30</x:v>
+        <x:v>筑波大学附属小学校</x:v>
       </x:c>
       <x:c r="C12" s="17" t="str">
         <x:v>必須</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
-        <x:v>dateRange。画面に出す表記</x:v>
+        <x:v>venueName。オンラインの場合も資料表記に従う</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
-        <x:v>主催</x:v>
+        <x:v>開催日（表示用）</x:v>
       </x:c>
       <x:c r="B13" s="25" t="str">
-        <x:v>東洋館出版社</x:v>
+        <x:v>2026年9月6日(日) 10:00〜15:30</x:v>
       </x:c>
       <x:c r="C13" s="17" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="D13" s="17" t="str">
-        <x:v>organizer。複数はセル内改行で1団体ずつ</x:v>
+        <x:v>dateRange。画面に出す表記</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
-        <x:v>共催</x:v>
-      </x:c>
-      <x:c r="B14" s="25"/>
+        <x:v>主催</x:v>
+      </x:c>
+      <x:c r="B14" s="25" t="str">
+        <x:v>東洋館出版社</x:v>
+      </x:c>
       <x:c r="C14" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>coOrganizer。複数はセル内改行</x:v>
+        <x:v>organizer。複数はセル内改行で1団体ずつ</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
-        <x:v>協力</x:v>
+        <x:v>共催</x:v>
       </x:c>
       <x:c r="B15" s="25"/>
       <x:c r="C15" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D15" s="17" t="str">
-        <x:v>cooperation。複数はセル内改行</x:v>
+        <x:v>coOrganizer。複数はセル内改行</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
-        <x:v>後援</x:v>
+        <x:v>協力</x:v>
       </x:c>
       <x:c r="B16" s="25"/>
       <x:c r="C16" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D16" s="17" t="str">
-        <x:v>support。複数はセル内改行</x:v>
+        <x:v>cooperation。複数はセル内改行</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
-        <x:v>ブランド色</x:v>
-      </x:c>
-      <x:c r="B17" s="25" t="str">
-        <x:v>#9B6BB5</x:v>
-      </x:c>
+        <x:v>後援</x:v>
+      </x:c>
+      <x:c r="B17" s="25"/>
       <x:c r="C17" s="17" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>brandColor。# + 6桁16進</x:v>
+        <x:v>support。複数はセル内改行</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="17" t="str">
-        <x:v>補助ブランド色</x:v>
+        <x:v>ブランド色</x:v>
       </x:c>
       <x:c r="B18" s="25" t="str">
-        <x:v>#5EBCE1</x:v>
+        <x:v>#9B6BB5</x:v>
       </x:c>
       <x:c r="C18" s="17" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="D18" s="17" t="str">
-        <x:v>brandColor2。# + 6桁16進</x:v>
+        <x:v>brandColor。# + 6桁16進</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="17" t="str">
-        <x:v>イベントID</x:v>
+        <x:v>補助ブランド色</x:v>
       </x:c>
       <x:c r="B19" s="25" t="str">
-        <x:v>2026-kokugo-sansu-day3</x:v>
+        <x:v>#5EBCE1</x:v>
       </x:c>
       <x:c r="C19" s="17" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="D19" s="17" t="str">
-        <x:v>半角英数・ハイフン・アンダースコアのみ</x:v>
+        <x:v>brandColor2。# + 6桁16進</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="17" t="str">
-        <x:v>並び順日付</x:v>
+        <x:v>イベントID</x:v>
       </x:c>
       <x:c r="B20" s="25" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>2026-kokugo-sansu-day3</x:v>
       </x:c>
       <x:c r="C20" s="17" t="str">
         <x:v>必須</x:v>
       </x:c>
       <x:c r="D20" s="17" t="str">
-        <x:v>sortDate。YYYY-MM-DD</x:v>
+        <x:v>半角英数・ハイフン・アンダースコアのみ</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="17" t="str">
-        <x:v>LINE追加ポップアップ</x:v>
+        <x:v>並び順日付</x:v>
       </x:c>
       <x:c r="B21" s="25" t="str">
-        <x:v>false</x:v>
+        <x:v>2026-09-06</x:v>
       </x:c>
       <x:c r="C21" s="17" t="str">
         <x:v>必須</x:v>
       </x:c>
       <x:c r="D21" s="17" t="str">
-        <x:v>linePromo。true / false</x:v>
+        <x:v>sortDate。YYYY-MM-DD</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="17" t="str">
-        <x:v>会場マップ補足</x:v>
+        <x:v>LINE追加ポップアップ</x:v>
       </x:c>
       <x:c r="B22" s="25" t="str">
-        <x:v>筑波大学附属小学校（東京都文京区大塚3-29-1）</x:v>
+        <x:v>false</x:v>
       </x:c>
       <x:c r="C22" s="17" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="D22" s="17" t="str">
-        <x:v>venue.mapNote</x:v>
+        <x:v>linePromo。true / false</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="17" t="str">
-        <x:v>会場マップ画像</x:v>
-      </x:c>
-      <x:c r="B23" s="25"/>
+        <x:v>会場マップ補足</x:v>
+      </x:c>
+      <x:c r="B23" s="25" t="str">
+        <x:v>筑波大学附属小学校（東京都文京区大塚3-29-1）</x:v>
+      </x:c>
       <x:c r="C23" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D23" s="17" t="str">
-        <x:v>venue.mapImage。相対パスまたは公開URL</x:v>
+        <x:v>venue.mapNote</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="17" t="str">
-        <x:v>書籍特設販売URL</x:v>
+        <x:v>会場マップ画像</x:v>
       </x:c>
       <x:c r="B24" s="25"/>
       <x:c r="C24" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D24" s="17" t="str">
-        <x:v>bookSale.url</x:v>
+        <x:v>venue.mapImage。相対パスまたは公開URL</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="17" t="str">
-        <x:v>書籍特設販売ラベル</x:v>
+        <x:v>書籍特設販売URL</x:v>
       </x:c>
       <x:c r="B25" s="25"/>
       <x:c r="C25" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D25" s="17" t="str">
-        <x:v>bookSale.label</x:v>
+        <x:v>bookSale.url</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="18" t="str">
-        <x:v>書籍特設販売補足</x:v>
+        <x:v>書籍特設販売ラベル</x:v>
       </x:c>
       <x:c r="B26" s="26"/>
       <x:c r="C26" s="18" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D26" s="18" t="str">
+        <x:v>bookSale.label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>書籍特設販売補足</x:v>
+      </x:c>
+      <x:c r="B27"/>
+      <x:c r="C27" t="str">
+        <x:v>任意</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
         <x:v>bookSale.note</x:v>
       </x:c>
     </x:row>
@@ -1998,7 +2012,7 @@
     <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd42042ba99694259"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4383f6df6f34fc9"/>
 </x:worksheet>
 </file>
 
@@ -2139,7 +2153,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra541ef464ec84236"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ded31b59e6c4d53"/>
 </x:worksheet>
 </file>
 
@@ -2705,7 +2719,7 @@
     <x:mergeCell ref="A1:G1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reeee7caadc184caa"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04b99d3e42f546a1"/>
 </x:worksheet>
 </file>
 
@@ -3604,7 +3618,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd7c792bf79f4298"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8036e9172f2d4b9e"/>
 </x:worksheet>
 </file>
 
@@ -3907,7 +3921,7 @@
       <x:c r="F4" s="24" t="str">
         <x:v>https://www.toyokan.co.jp/products/5984</x:v>
       </x:c>
-      <x:c r="G4" s="24"/>
+      <x:c r="G4" s="24" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
@@ -3928,7 +3942,7 @@
       <x:c r="F5" s="25" t="str">
         <x:v>https://www.toyokan.co.jp/products/5777</x:v>
       </x:c>
-      <x:c r="G5" s="25"/>
+      <x:c r="G5" s="25" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="25" t="str">
@@ -3949,7 +3963,7 @@
       <x:c r="F6" s="25" t="str">
         <x:v>https://www.toyokan.co.jp/products/5084</x:v>
       </x:c>
-      <x:c r="G6" s="25"/>
+      <x:c r="G6" s="25" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="25" t="str">
@@ -3970,7 +3984,7 @@
       <x:c r="F7" s="25" t="str">
         <x:v>https://www.toyokan.co.jp/products/4345</x:v>
       </x:c>
-      <x:c r="G7" s="25"/>
+      <x:c r="G7" s="25" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="25" t="str">
@@ -3991,7 +4005,7 @@
       <x:c r="F8" s="25" t="str">
         <x:v>https://www.toyokan.co.jp/products/4034</x:v>
       </x:c>
-      <x:c r="G8" s="25"/>
+      <x:c r="G8" s="25" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="25" t="str">
@@ -4012,7 +4026,7 @@
       <x:c r="F9" s="25" t="str">
         <x:v>https://www.toyokan.co.jp/products/3729</x:v>
       </x:c>
-      <x:c r="G9" s="25"/>
+      <x:c r="G9" s="25" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="25" t="str">
@@ -4033,7 +4047,7 @@
       <x:c r="F10" s="25" t="str">
         <x:v>https://www.toyokan.co.jp/products/6346</x:v>
       </x:c>
-      <x:c r="G10" s="25"/>
+      <x:c r="G10" s="25" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="25"/>
